--- a/registration_forms/033_online_chat_room_registration_form--registration_forms.xlsx
+++ b/registration_forms/033_online_chat_room_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1269,8 +1269,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'option 1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'option 2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3', 'label': 'option 3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_multiple_option1',_'label':_'select_multiple_option_1'}</t>
+          <t>select_multiple_option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_multiple_option1', 'label': 'select_multiple_option 1'}</t>
+          <t>select multiple option 1</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_multiple_option2',_'label':_'select_multiple_option_2'}</t>
+          <t>select_multiple_option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_multiple_option2', 'label': 'select_multiple_option 2'}</t>
+          <t>select multiple option 2</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'select_multiple_option3',_'label':_'select_multiple_option_3'}</t>
+          <t>select_multiple_option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'select_multiple_option3', 'label': 'select_multiple_option 3'}</t>
+          <t>select multiple option 3</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'select_multiple_option4',_'label':_'select_multiple_option_4'}</t>
+          <t>select_multiple_option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'select_multiple_option4', 'label': 'select_multiple_option 4'}</t>
+          <t>select multiple option 4</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'select_multiple_option5',_'label':_'select_multiple_option_5'}</t>
+          <t>select_multiple_option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'select_multiple_option5', 'label': 'select_multiple_option 5'}</t>
+          <t>select multiple option 5</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'select_multiple_option6',_'label':_'select_multiple_option_6'}</t>
+          <t>select_multiple_option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'select_multiple_option6', 'label': 'select_multiple_option 6'}</t>
+          <t>select multiple option 6</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'select_one_option1',_'label':_'select_one_option_1'}</t>
+          <t>select_one_option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'select_one_option1', 'label': 'select_one_option 1'}</t>
+          <t>select one option 1</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'select_one_option2',_'label':_'select_one_option_2'}</t>
+          <t>select_one_option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'select_one_option2', 'label': 'select_one_option 2'}</t>
+          <t>select one option 2</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'select_one_option3',_'label':_'select_one_option_3'}</t>
+          <t>select_one_option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'select_one_option3', 'label': 'select_one_option 3'}</t>
+          <t>select one option 3</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'select_multiple_option4',_'label':_'select_multiple_option_4'}</t>
+          <t>select_multiple_option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'select_multiple_option4', 'label': 'select_multiple_option 4'}</t>
+          <t>select multiple option 4</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'select_multiple_option5',_'label':_'select_multiple_option_5'}</t>
+          <t>select_multiple_option_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'select_multiple_option5', 'label': 'select_multiple_option 5'}</t>
+          <t>select multiple option 5</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'select_multiple_option6',_'label':_'select_multiple_option_6'}</t>
+          <t>select_multiple_option_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'select_multiple_option6', 'label': 'select_multiple_option 6'}</t>
+          <t>select multiple option 6</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'select_multiple_option7',_'label':_'select_multiple_option_7'}</t>
+          <t>select_multiple_option_7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'select_multiple_option7', 'label': 'select_multiple_option 7'}</t>
+          <t>select multiple option 7</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'select_multiple_option8',_'label':_'select_multiple_option_8'}</t>
+          <t>select_multiple_option_8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'select_multiple_option8', 'label': 'select_multiple_option 8'}</t>
+          <t>select multiple option 8</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'select_multiple_option9',_'label':_'select_multiple_option_9'}</t>
+          <t>select_multiple_option_9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'select_multiple_option9', 'label': 'select_multiple_option 9'}</t>
+          <t>select multiple option 9</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'select_multiple_option10',_'label':_'select_multiple_option_10'}</t>
+          <t>select_multiple_option_10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'select_multiple_option10', 'label': 'select_multiple_option 10'}</t>
+          <t>select multiple option 10</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'select_multiple_option11',_'label':_'select_multiple_option_11'}</t>
+          <t>select_multiple_option_11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'select_multiple_option11', 'label': 'select_multiple_option 11'}</t>
+          <t>select multiple option 11</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'select_multiple_option12',_'label':_'select_multiple_option_12'}</t>
+          <t>select_multiple_option_12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'select_multiple_option12', 'label': 'select_multiple_option 12'}</t>
+          <t>select multiple option 12</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'select_multiple_option13',_'label':_'select_multiple_option_13'}</t>
+          <t>select_multiple_option_13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'select_multiple_option13', 'label': 'select_multiple_option 13'}</t>
+          <t>select multiple option 13</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'select_multiple_option14',_'label':_'select_multiple_option_14'}</t>
+          <t>select_multiple_option_14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'select_multiple_option14', 'label': 'select_multiple_option 14'}</t>
+          <t>select multiple option 14</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'select_multiple_option15',_'label':_'select_multiple_option_15'}</t>
+          <t>select_multiple_option_15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'select_multiple_option15', 'label': 'select_multiple_option 15'}</t>
+          <t>select multiple option 15</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'select_multiple_option16',_'label':_'select_multiple_option_16'}</t>
+          <t>select_multiple_option_16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'select_multiple_option16', 'label': 'select_multiple_option 16'}</t>
+          <t>select multiple option 16</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'select_multiple_option17',_'label':_'select_multiple_option_17'}</t>
+          <t>select_multiple_option_17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'select_multiple_option17', 'label': 'select_multiple_option 17'}</t>
+          <t>select multiple option 17</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'select_one_option4',_'label':_'select_one_option_4'}</t>
+          <t>select_one_option_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'select_one_option4', 'label': 'select_one_option 4'}</t>
+          <t>select one option 4</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'select_one_option5',_'label':_'select_one_option_5'}</t>
+          <t>select_one_option_5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'select_one_option5', 'label': 'select_one_option 5'}</t>
+          <t>select one option 5</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'select_one_option6',_'label':_'select_one_option_6'}</t>
+          <t>select_one_option_6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'select_one_option6', 'label': 'select_one_option 6'}</t>
+          <t>select one option 6</t>
         </is>
       </c>
     </row>
